--- a/site/public/downloads/ken/ken-blue-collar.xlsx
+++ b/site/public/downloads/ken/ken-blue-collar.xlsx
@@ -581,7 +581,7 @@
       </c>
       <c r="B5" s="4" t="inlineStr">
         <is>
-          <t>台灣個人／家庭通膨每年 10% 起跳。官方 CPI 約 2% 左右，但房租、外食、醫療與照護的實際漲幅常遠高於 CPI；本工具採保守的 10% 起跳假設，讓規劃留足安全邊際。通膨格子設有驗證，低於 10% 會被拒絕，公式也以 MAX(10%, 輸入值) 計算。</t>
+          <t>台灣個人／家庭通膨每年 5% 起跳。官方 CPI 約 2% 左右，但房租、外食、醫療與照護的實際漲幅常遠高於 CPI；本工具採保守的 5% 起跳假設，讓規劃留足安全邊際。通膨格子設有驗證，低於 5% 會被拒絕，公式也以 MAX(5%, 輸入值) 計算。</t>
         </is>
       </c>
     </row>
@@ -1279,15 +1279,15 @@
     <row r="16">
       <c r="A16" s="4" t="inlineStr">
         <is>
-          <t>個人／家庭通膨（10% 起跳）</t>
+          <t>個人／家庭通膨（5% 起跳）</t>
         </is>
       </c>
       <c r="B16" s="22" t="n">
-        <v>0.1</v>
+        <v>0.05</v>
       </c>
       <c r="C16" s="11" t="inlineStr">
         <is>
-          <t>不可低於 10%</t>
+          <t>不可低於 5%</t>
         </is>
       </c>
     </row>
@@ -1373,7 +1373,7 @@
         </is>
       </c>
       <c r="B25" s="18">
-        <f>$B$19*(1+MAX(0.1,$B$16))</f>
+        <f>$B$19*(1+MAX(0.05,$B$16))</f>
         <v/>
       </c>
     </row>
@@ -1415,8 +1415,8 @@
     <mergeCell ref="A2:C2"/>
   </mergeCells>
   <dataValidations count="1">
-    <dataValidation sqref="B16" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="0" errorTitle="通膨假設" error="本工具假設台灣個人通膨每年 10% 起跳，請輸入 10% 以上。" type="decimal" operator="greaterThanOrEqual">
-      <formula1>0.1</formula1>
+    <dataValidation sqref="B16" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="0" errorTitle="通膨假設" error="本工具假設台灣個人通膨每年 5% 起跳，請輸入 5% 以上。" type="decimal" operator="greaterThanOrEqual">
+      <formula1>0.05</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -1470,15 +1470,15 @@
     <row r="5">
       <c r="A5" s="4" t="inlineStr">
         <is>
-          <t>個人／家庭通膨（10% 起跳）</t>
+          <t>個人／家庭通膨（5% 起跳）</t>
         </is>
       </c>
       <c r="B5" s="22" t="n">
-        <v>0.1</v>
+        <v>0.05</v>
       </c>
       <c r="C5" s="11" t="inlineStr">
         <is>
-          <t>不可低於 10%</t>
+          <t>不可低於 5%</t>
         </is>
       </c>
     </row>
@@ -1551,7 +1551,7 @@
         <v/>
       </c>
       <c r="H7" s="17">
-        <f>IF(E7&gt;0,E7*(1-(1+MAX(0.1,$B$5))^(-$B$4))/((1+MAX(0.1,$B$5))^(1/12)-1)-(B7+D7),"")</f>
+        <f>IF(E7&gt;0,E7*(1-(1+MAX(0.05,$B$5))^(-$B$4))/((1+MAX(0.05,$B$5))^(1/12)-1)-(B7+D7),"")</f>
         <v/>
       </c>
     </row>
@@ -1582,7 +1582,7 @@
         <v/>
       </c>
       <c r="H8" s="17">
-        <f>IF(E8&gt;0,E8*(1-(1+MAX(0.1,$B$5))^(-$B$4))/((1+MAX(0.1,$B$5))^(1/12)-1)-(B8+D8),"")</f>
+        <f>IF(E8&gt;0,E8*(1-(1+MAX(0.05,$B$5))^(-$B$4))/((1+MAX(0.05,$B$5))^(1/12)-1)-(B8+D8),"")</f>
         <v/>
       </c>
     </row>
@@ -1613,7 +1613,7 @@
         <v/>
       </c>
       <c r="H9" s="17">
-        <f>IF(E9&gt;0,E9*(1-(1+MAX(0.1,$B$5))^(-$B$4))/((1+MAX(0.1,$B$5))^(1/12)-1)-(B9+D9),"")</f>
+        <f>IF(E9&gt;0,E9*(1-(1+MAX(0.05,$B$5))^(-$B$4))/((1+MAX(0.05,$B$5))^(1/12)-1)-(B9+D9),"")</f>
         <v/>
       </c>
     </row>
@@ -1632,7 +1632,7 @@
         <v/>
       </c>
       <c r="H10" s="17">
-        <f>IF(E10&gt;0,E10*(1-(1+MAX(0.1,$B$5))^(-$B$4))/((1+MAX(0.1,$B$5))^(1/12)-1)-(B10+D10),"")</f>
+        <f>IF(E10&gt;0,E10*(1-(1+MAX(0.05,$B$5))^(-$B$4))/((1+MAX(0.05,$B$5))^(1/12)-1)-(B10+D10),"")</f>
         <v/>
       </c>
     </row>
@@ -1651,7 +1651,7 @@
         <v/>
       </c>
       <c r="H11" s="17">
-        <f>IF(E11&gt;0,E11*(1-(1+MAX(0.1,$B$5))^(-$B$4))/((1+MAX(0.1,$B$5))^(1/12)-1)-(B11+D11),"")</f>
+        <f>IF(E11&gt;0,E11*(1-(1+MAX(0.05,$B$5))^(-$B$4))/((1+MAX(0.05,$B$5))^(1/12)-1)-(B11+D11),"")</f>
         <v/>
       </c>
     </row>
@@ -1670,7 +1670,7 @@
         <v/>
       </c>
       <c r="H12" s="17">
-        <f>IF(E12&gt;0,E12*(1-(1+MAX(0.1,$B$5))^(-$B$4))/((1+MAX(0.1,$B$5))^(1/12)-1)-(B12+D12),"")</f>
+        <f>IF(E12&gt;0,E12*(1-(1+MAX(0.05,$B$5))^(-$B$4))/((1+MAX(0.05,$B$5))^(1/12)-1)-(B12+D12),"")</f>
         <v/>
       </c>
     </row>
@@ -1689,7 +1689,7 @@
         <v/>
       </c>
       <c r="H13" s="17">
-        <f>IF(E13&gt;0,E13*(1-(1+MAX(0.1,$B$5))^(-$B$4))/((1+MAX(0.1,$B$5))^(1/12)-1)-(B13+D13),"")</f>
+        <f>IF(E13&gt;0,E13*(1-(1+MAX(0.05,$B$5))^(-$B$4))/((1+MAX(0.05,$B$5))^(1/12)-1)-(B13+D13),"")</f>
         <v/>
       </c>
     </row>
@@ -1698,8 +1698,8 @@
     <mergeCell ref="A2:H2"/>
   </mergeCells>
   <dataValidations count="1">
-    <dataValidation sqref="B5" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="0" errorTitle="通膨假設" error="本工具假設台灣個人通膨每年 10% 起跳，請輸入 10% 以上。" type="decimal" operator="greaterThanOrEqual">
-      <formula1>0.1</formula1>
+    <dataValidation sqref="B5" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="0" errorTitle="通膨假設" error="本工具假設台灣個人通膨每年 5% 起跳，請輸入 5% 以上。" type="decimal" operator="greaterThanOrEqual">
+      <formula1>0.05</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
